--- a/LED/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/LED/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,17 +15,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
   <si>
     <t>atk_f407</t>
   </si>
   <si>
+    <t>heap_4.o</t>
+  </si>
+  <si>
     <t>malloc.o</t>
   </si>
   <si>
-    <t>heap_4.o</t>
-  </si>
-  <si>
     <t>usbd_cdc_interface.o</t>
   </si>
   <si>
@@ -47,6 +47,9 @@
     <t>usart.o</t>
   </si>
   <si>
+    <t>can.o</t>
+  </si>
+  <si>
     <t>queue.o</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
   </si>
   <si>
     <t>usbd_core.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_can.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_gpio.o</t>
@@ -308,14 +314,14 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$60</c:f>
+              <c:f>ram_percent!$A$3:$A$62</c:f>
               <c:strCache>
-                <c:ptCount val="58"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
+                  <c:v>heap_4.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>malloc.o</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>usbd_cdc_interface.o</c:v>
@@ -339,36 +345,39 @@
                   <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>can.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="59">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -376,68 +385,71 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$60</c:f>
+              <c:f>ram_percent!$B$3:$B$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>69.16863250732422</c:v>
+                  <c:v>55.02119827270508</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.38621139526367</c:v>
+                  <c:v>38.98826599121094</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.683231830596924</c:v>
+                  <c:v>1.51245653629303</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.050132036209106</c:v>
+                  <c:v>1.15559732913971</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.032270193099976</c:v>
+                  <c:v>1.14552915096283</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.595649719238281</c:v>
+                  <c:v>0.8994194269180298</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.662869393825531</c:v>
+                  <c:v>0.3736394047737122</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.5378371477127075</c:v>
+                  <c:v>0.3031625151634216</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5378371477127075</c:v>
+                  <c:v>0.3031625151634216</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1270168870687485</c:v>
+                  <c:v>0.1029186397790909</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1190783306956291</c:v>
+                  <c:v>0.07159557193517685</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.02381566725671291</c:v>
+                  <c:v>0.06712085008621216</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.02381566725671291</c:v>
+                  <c:v>0.01342417020350695</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.0178617499768734</c:v>
+                  <c:v>0.01342417020350695</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.00793855544179678</c:v>
+                  <c:v>0.01006812788546085</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.00793855544179678</c:v>
+                  <c:v>0.004474723245948553</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.00793855544179678</c:v>
+                  <c:v>0.004474723245948553</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00793855544179678</c:v>
+                  <c:v>0.004474723245948553</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.001984638860449195</c:v>
-                </c:pt>
-                <c:pt idx="57">
+                  <c:v>0.004474723245948553</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.001118680811487138</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -505,9 +517,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$60</c:f>
+              <c:f>flash_percent!$A$3:$A$62</c:f>
               <c:strCache>
-                <c:ptCount val="58"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>tasks.o</c:v>
                 </c:pt>
@@ -557,129 +569,135 @@
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>stm32f4xx_hal_can.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>malloc.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>usbd_desc.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>usbd_cdc_interface.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
+                  <c:v>can.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>sys.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="35">
                   <c:v>led.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="36">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="37">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="38">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="41">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="42">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="43">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="50">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="51">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="52">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="53">
                   <c:v>fputc.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="54">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="55">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="56">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="57">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="58">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="59">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -687,182 +705,188 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$60</c:f>
+              <c:f>flash_percent!$B$3:$B$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>10.76172733306885</c:v>
+                  <c:v>10.45248794555664</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.21205520629883</c:v>
+                  <c:v>9.918609619140625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.697760581970215</c:v>
+                  <c:v>8.447829246520996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.350523948669434</c:v>
+                  <c:v>7.139305591583252</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.976342678070068</c:v>
+                  <c:v>5.804611206054688</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.828146457672119</c:v>
+                  <c:v>5.66067361831665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.903942108154297</c:v>
+                  <c:v>4.763026237487793</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.839274883270264</c:v>
+                  <c:v>4.700217247009277</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.241101264953613</c:v>
+                  <c:v>4.119232654571533</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.365397453308106</c:v>
+                  <c:v>3.268692255020142</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.163311958312988</c:v>
+                  <c:v>3.072413682937622</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.96931004524231</c:v>
+                  <c:v>2.883986234664917</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.872308969497681</c:v>
+                  <c:v>2.789772510528565</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.705251455307007</c:v>
+                  <c:v>2.627515554428101</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.371136903762817</c:v>
+                  <c:v>2.303001642227173</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.228329658508301</c:v>
+                  <c:v>2.164298295974731</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.552016854286194</c:v>
+                  <c:v>1.983721971511841</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.476571559906006</c:v>
+                  <c:v>1.507419347763062</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.379570484161377</c:v>
+                  <c:v>1.434141993522644</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.196346282958984</c:v>
+                  <c:v>1.339928269386292</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.172096014022827</c:v>
+                  <c:v>1.161969065666199</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.153234720230103</c:v>
+                  <c:v>1.138415694236755</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9268989562988281</c:v>
+                  <c:v>1.120096325874329</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8999541997909546</c:v>
+                  <c:v>0.900264322757721</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6358957886695862</c:v>
+                  <c:v>0.8740938305854797</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6143400073051453</c:v>
+                  <c:v>0.837455153465271</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6008676290512085</c:v>
+                  <c:v>0.6176232099533081</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5981731414794922</c:v>
+                  <c:v>0.5966868400573731</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5658394694328308</c:v>
+                  <c:v>0.5836015939712524</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5496726036071777</c:v>
+                  <c:v>0.5809845328330994</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5011721253395081</c:v>
+                  <c:v>0.5495799779891968</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4688384234905243</c:v>
+                  <c:v>0.5338776707649231</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3987821042537689</c:v>
+                  <c:v>0.4867708384990692</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3987821042537689</c:v>
+                  <c:v>0.4553662538528442</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.2640584111213684</c:v>
+                  <c:v>0.3873230218887329</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.2425026297569275</c:v>
+                  <c:v>0.3873230218887329</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.231724739074707</c:v>
+                  <c:v>0.256470650434494</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2155578881502152</c:v>
+                  <c:v>0.2355342656373978</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1508905291557312</c:v>
+                  <c:v>0.2250660806894302</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1293347328901291</c:v>
+                  <c:v>0.2093637883663178</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1293347328901291</c:v>
+                  <c:v>0.1988956034183502</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1293347328901291</c:v>
+                  <c:v>0.1256182789802551</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1185568422079086</c:v>
+                  <c:v>0.1256182789802551</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.09700105339288712</c:v>
+                  <c:v>0.1256182789802551</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09700105339288712</c:v>
+                  <c:v>0.115150086581707</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.09700105339288712</c:v>
+                  <c:v>0.09421370923519135</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.09700105339288712</c:v>
+                  <c:v>0.09421370923519135</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.08622315526008606</c:v>
+                  <c:v>0.09421370923519135</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.08083420991897583</c:v>
+                  <c:v>0.09421370923519135</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.08083420991897583</c:v>
+                  <c:v>0.08374551683664322</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.05388947203755379</c:v>
+                  <c:v>0.07851142436265945</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.04850052669644356</c:v>
+                  <c:v>0.07851142436265945</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.02155578881502152</c:v>
+                  <c:v>0.05234094709157944</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.02155578881502152</c:v>
+                  <c:v>0.04710685461759567</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.01077789440751076</c:v>
+                  <c:v>0.02093637920916081</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.01077789440751076</c:v>
+                  <c:v>0.02093637920916081</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.01077789440751076</c:v>
+                  <c:v>0.0104681896045804</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>0.0104681896045804</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.0104681896045804</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -967,8 +991,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H60" totalsRowCount="1">
-  <autoFilter ref="A2:H59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H62" totalsRowCount="1">
+  <autoFilter ref="A2:H61"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -984,8 +1008,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H60" totalsRowCount="1">
-  <autoFilter ref="A2:H59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H62" totalsRowCount="1">
+  <autoFilter ref="A2:H61"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1285,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1298,28 +1322,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1327,25 +1351,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>69.16863250732422</v>
+        <v>55.02119827270508</v>
       </c>
       <c r="C3" s="1">
-        <v>34852</v>
+        <v>49184</v>
       </c>
       <c r="D3" s="1">
-        <v>576</v>
+        <v>880</v>
       </c>
       <c r="E3" s="1">
-        <v>504</v>
+        <v>848</v>
       </c>
       <c r="F3" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H3" s="1">
-        <v>34816</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1353,25 +1377,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>20.38621139526367</v>
+        <v>38.98826599121094</v>
       </c>
       <c r="C4" s="1">
-        <v>10272</v>
+        <v>34852</v>
       </c>
       <c r="D4" s="1">
-        <v>880</v>
+        <v>576</v>
       </c>
       <c r="E4" s="1">
-        <v>848</v>
+        <v>504</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H4" s="1">
-        <v>10240</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1379,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>2.683231830596924</v>
+        <v>1.51245653629303</v>
       </c>
       <c r="C5" s="1">
         <v>1352</v>
@@ -1405,7 +1429,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>2.050132036209106</v>
+        <v>1.15559732913971</v>
       </c>
       <c r="C6" s="1">
         <v>1033</v>
@@ -1431,7 +1455,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>2.032270193099976</v>
+        <v>1.14552915096283</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -1457,7 +1481,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>1.595649719238281</v>
+        <v>0.8994194269180298</v>
       </c>
       <c r="C8" s="1">
         <v>804</v>
@@ -1483,7 +1507,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.662869393825531</v>
+        <v>0.3736394047737122</v>
       </c>
       <c r="C9" s="1">
         <v>334</v>
@@ -1509,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.5378371477127075</v>
+        <v>0.3031625151634216</v>
       </c>
       <c r="C10" s="1">
         <v>271</v>
@@ -1535,7 +1559,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.5378371477127075</v>
+        <v>0.3031625151634216</v>
       </c>
       <c r="C11" s="1">
         <v>271</v>
@@ -1561,16 +1585,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1270168870687485</v>
+        <v>0.1029186397790909</v>
       </c>
       <c r="C12" s="1">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D12" s="1">
-        <v>1574</v>
+        <v>320</v>
       </c>
       <c r="E12" s="1">
-        <v>1574</v>
+        <v>320</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1579,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1587,25 +1611,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1190783306956291</v>
+        <v>0.07159557193517685</v>
       </c>
       <c r="C13" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D13" s="1">
-        <v>1102</v>
+        <v>1574</v>
       </c>
       <c r="E13" s="1">
-        <v>1082</v>
+        <v>1574</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1613,25 +1637,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.02381566725671291</v>
+        <v>0.06712085008621216</v>
       </c>
       <c r="C14" s="1">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D14" s="1">
-        <v>1174</v>
+        <v>1102</v>
       </c>
       <c r="E14" s="1">
-        <v>1162</v>
+        <v>1082</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1639,16 +1663,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.02381566725671291</v>
+        <v>0.01342417020350695</v>
       </c>
       <c r="C15" s="1">
         <v>12</v>
       </c>
       <c r="D15" s="1">
-        <v>236</v>
+        <v>1174</v>
       </c>
       <c r="E15" s="1">
-        <v>224</v>
+        <v>1162</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1665,22 +1689,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0178617499768734</v>
+        <v>0.01342417020350695</v>
       </c>
       <c r="C16" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E16" s="1">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1691,22 +1715,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.00793855544179678</v>
+        <v>0.01006812788546085</v>
       </c>
       <c r="C17" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1">
-        <v>2728</v>
+        <v>223</v>
       </c>
       <c r="E17" s="1">
-        <v>2724</v>
+        <v>214</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1717,16 +1741,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.00793855544179678</v>
+        <v>0.004474723245948553</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>4</v>
+        <v>2728</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>2724</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1743,19 +1767,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.00793855544179678</v>
+        <v>0.004474723245948553</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>4</v>
@@ -1769,19 +1793,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.00793855544179678</v>
+        <v>0.004474723245948553</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="E20" s="1">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G20" s="1">
         <v>4</v>
@@ -1795,56 +1819,82 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.001984638860449195</v>
+        <v>0.004474723245948553</v>
       </c>
       <c r="C21" s="1">
+        <v>4</v>
+      </c>
+      <c r="D21" s="1">
+        <v>80</v>
+      </c>
+      <c r="E21" s="1">
+        <v>76</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.001118680811487138</v>
+      </c>
+      <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D22" s="1">
         <v>2163</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E22" s="1">
         <v>2162</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
         <v>1</v>
       </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60">
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C60">
+      <c r="C62">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D60">
+      <c r="D62">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E60">
+      <c r="E62">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F60">
+      <c r="F62">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G60">
+      <c r="G62">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H60">
+      <c r="H62">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1860,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1873,28 +1923,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>65</v>
-      </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1902,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>10.76172733306885</v>
+        <v>10.45248794555664</v>
       </c>
       <c r="C3" s="1">
         <v>3994</v>
@@ -1925,10 +1975,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
-        <v>10.21205520629883</v>
+        <v>9.918609619140625</v>
       </c>
       <c r="C4" s="1">
         <v>3790</v>
@@ -1951,10 +2001,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>8.697760581970215</v>
+        <v>8.447829246520996</v>
       </c>
       <c r="C5" s="1">
         <v>3228</v>
@@ -1977,10 +2027,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>7.350523948669434</v>
+        <v>7.139305591583252</v>
       </c>
       <c r="C6" s="1">
         <v>2728</v>
@@ -2003,10 +2053,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>5.976342678070068</v>
+        <v>5.804611206054688</v>
       </c>
       <c r="C7" s="1">
         <v>2218</v>
@@ -2029,10 +2079,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>5.828146457672119</v>
+        <v>5.66067361831665</v>
       </c>
       <c r="C8" s="1">
         <v>2163</v>
@@ -2055,10 +2105,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>4.903942108154297</v>
+        <v>4.763026237487793</v>
       </c>
       <c r="C9" s="1">
         <v>1820</v>
@@ -2081,10 +2131,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2">
-        <v>4.839274883270264</v>
+        <v>4.700217247009277</v>
       </c>
       <c r="C10" s="1">
         <v>1796</v>
@@ -2107,10 +2157,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>4.241101264953613</v>
+        <v>4.119232654571533</v>
       </c>
       <c r="C11" s="1">
         <v>1574</v>
@@ -2136,7 +2186,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2">
-        <v>3.365397453308106</v>
+        <v>3.268692255020142</v>
       </c>
       <c r="C12" s="1">
         <v>1249</v>
@@ -2159,10 +2209,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>3.163311958312988</v>
+        <v>3.072413682937622</v>
       </c>
       <c r="C13" s="1">
         <v>1174</v>
@@ -2185,10 +2235,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2.96931004524231</v>
+        <v>2.883986234664917</v>
       </c>
       <c r="C14" s="1">
         <v>1102</v>
@@ -2211,10 +2261,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2">
-        <v>2.872308969497681</v>
+        <v>2.789772510528565</v>
       </c>
       <c r="C15" s="1">
         <v>1066</v>
@@ -2237,10 +2287,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2">
-        <v>2.705251455307007</v>
+        <v>2.627515554428101</v>
       </c>
       <c r="C16" s="1">
         <v>1004</v>
@@ -2263,16 +2313,16 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>2.371136903762817</v>
+        <v>2.303001642227173</v>
       </c>
       <c r="C17" s="1">
         <v>880</v>
       </c>
       <c r="D17" s="1">
-        <v>10272</v>
+        <v>49184</v>
       </c>
       <c r="E17" s="1">
         <v>848</v>
@@ -2284,7 +2334,7 @@
         <v>32</v>
       </c>
       <c r="H17" s="1">
-        <v>10240</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2292,7 +2342,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>2.228329658508301</v>
+        <v>2.164298295974731</v>
       </c>
       <c r="C18" s="1">
         <v>827</v>
@@ -2315,201 +2365,201 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>1.552016854286194</v>
+        <v>1.983721971511841</v>
       </c>
       <c r="C19" s="1">
-        <v>576</v>
+        <v>758</v>
       </c>
       <c r="D19" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>504</v>
+        <v>758</v>
       </c>
       <c r="F19" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="B20" s="2">
-        <v>1.476571559906006</v>
+        <v>1.507419347763062</v>
       </c>
       <c r="C20" s="1">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>34852</v>
       </c>
       <c r="E20" s="1">
-        <v>548</v>
+        <v>504</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2">
-        <v>1.379570484161377</v>
+        <v>1.434141993522644</v>
       </c>
       <c r="C21" s="1">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D21" s="1">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>434</v>
+        <v>548</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2">
-        <v>1.196346282958984</v>
+        <v>1.339928269386292</v>
       </c>
       <c r="C22" s="1">
-        <v>444</v>
+        <v>512</v>
       </c>
       <c r="D22" s="1">
-        <v>1024</v>
+        <v>334</v>
       </c>
       <c r="E22" s="1">
-        <v>52</v>
+        <v>434</v>
       </c>
       <c r="F22" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H22" s="1">
-        <v>1024</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2">
-        <v>1.172096014022827</v>
+        <v>1.161969065666199</v>
       </c>
       <c r="C23" s="1">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D23" s="1">
-        <v>271</v>
+        <v>1024</v>
       </c>
       <c r="E23" s="1">
-        <v>432</v>
+        <v>52</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>268</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1.138415694236755</v>
+      </c>
+      <c r="C24" s="1">
+        <v>435</v>
+      </c>
+      <c r="D24" s="1">
+        <v>271</v>
+      </c>
+      <c r="E24" s="1">
+        <v>432</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="B24" s="2">
-        <v>1.153234720230103</v>
-      </c>
-      <c r="C24" s="1">
-        <v>428</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1352</v>
-      </c>
-      <c r="E24" s="1">
-        <v>396</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>32</v>
-      </c>
       <c r="H24" s="1">
-        <v>1320</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9268989562988281</v>
+        <v>1.120096325874329</v>
       </c>
       <c r="C25" s="1">
-        <v>344</v>
+        <v>428</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="E25" s="1">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8999541997909546</v>
+        <v>0.900264322757721</v>
       </c>
       <c r="C26" s="1">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2523,25 +2573,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6358957886695862</v>
+        <v>0.8740938305854797</v>
       </c>
       <c r="C27" s="1">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="D27" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>224</v>
+        <v>334</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2549,19 +2599,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6143400073051453</v>
+        <v>0.837455153465271</v>
       </c>
       <c r="C28" s="1">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E28" s="1">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2570,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2578,22 +2628,22 @@
         <v>14</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6008676290512085</v>
+        <v>0.6176232099533081</v>
       </c>
       <c r="C29" s="1">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D29" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2601,19 +2651,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5981731414794922</v>
+        <v>0.5966868400573731</v>
       </c>
       <c r="C30" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2627,25 +2677,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5658394694328308</v>
+        <v>0.5836015939712524</v>
       </c>
       <c r="C31" s="1">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2656,16 +2706,16 @@
         <v>33</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5496726036071777</v>
+        <v>0.5809845328330994</v>
       </c>
       <c r="C32" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2682,16 +2732,16 @@
         <v>34</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5011721253395081</v>
+        <v>0.5495799779891968</v>
       </c>
       <c r="C33" s="1">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2708,16 +2758,16 @@
         <v>35</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4688384234905243</v>
+        <v>0.5338776707649231</v>
       </c>
       <c r="C34" s="1">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2734,16 +2784,16 @@
         <v>36</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3987821042537689</v>
+        <v>0.4867708384990692</v>
       </c>
       <c r="C35" s="1">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2760,16 +2810,16 @@
         <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3987821042537689</v>
+        <v>0.4553662538528442</v>
       </c>
       <c r="C36" s="1">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2786,16 +2836,16 @@
         <v>38</v>
       </c>
       <c r="B37" s="2">
-        <v>0.2640584111213684</v>
+        <v>0.3873230218887329</v>
       </c>
       <c r="C37" s="1">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2812,16 +2862,16 @@
         <v>39</v>
       </c>
       <c r="B38" s="2">
-        <v>0.2425026297569275</v>
+        <v>0.3873230218887329</v>
       </c>
       <c r="C38" s="1">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2838,16 +2888,16 @@
         <v>40</v>
       </c>
       <c r="B39" s="2">
-        <v>0.231724739074707</v>
+        <v>0.256470650434494</v>
       </c>
       <c r="C39" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2861,25 +2911,25 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2155578881502152</v>
+        <v>0.2355342656373978</v>
       </c>
       <c r="C40" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -2887,19 +2937,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1508905291557312</v>
+        <v>0.2250660806894302</v>
       </c>
       <c r="C41" s="1">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2913,25 +2963,25 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1293347328901291</v>
+        <v>0.2093637883663178</v>
       </c>
       <c r="C42" s="1">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E42" s="1">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -2942,16 +2992,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1293347328901291</v>
+        <v>0.1988956034183502</v>
       </c>
       <c r="C43" s="1">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2965,25 +3015,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1293347328901291</v>
+        <v>0.1256182789802551</v>
       </c>
       <c r="C44" s="1">
         <v>48</v>
       </c>
       <c r="D44" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F44" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -2991,19 +3041,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1185568422079086</v>
+        <v>0.1256182789802551</v>
       </c>
       <c r="C45" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3017,25 +3067,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B46" s="2">
-        <v>0.09700105339288712</v>
+        <v>0.1256182789802551</v>
       </c>
       <c r="C46" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46" s="1">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -3046,16 +3096,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0.09700105339288712</v>
+        <v>0.115150086581707</v>
       </c>
       <c r="C47" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3072,7 +3122,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0.09700105339288712</v>
+        <v>0.09421370923519135</v>
       </c>
       <c r="C48" s="1">
         <v>36</v>
@@ -3098,7 +3148,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.09700105339288712</v>
+        <v>0.09421370923519135</v>
       </c>
       <c r="C49" s="1">
         <v>36</v>
@@ -3124,16 +3174,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.08622315526008606</v>
+        <v>0.09421370923519135</v>
       </c>
       <c r="C50" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3150,16 +3200,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.08083420991897583</v>
+        <v>0.09421370923519135</v>
       </c>
       <c r="C51" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3176,16 +3226,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.08083420991897583</v>
+        <v>0.08374551683664322</v>
       </c>
       <c r="C52" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3202,16 +3252,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.05388947203755379</v>
+        <v>0.07851142436265945</v>
       </c>
       <c r="C53" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3228,16 +3278,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.04850052669644356</v>
+        <v>0.07851142436265945</v>
       </c>
       <c r="C54" s="1">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3254,16 +3304,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.02155578881502152</v>
+        <v>0.05234094709157944</v>
       </c>
       <c r="C55" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3280,16 +3330,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.02155578881502152</v>
+        <v>0.04710685461759567</v>
       </c>
       <c r="C56" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3303,25 +3353,25 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.01077789440751076</v>
+        <v>0.02093637920916081</v>
       </c>
       <c r="C57" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D57" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -3329,19 +3379,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.01077789440751076</v>
+        <v>0.02093637920916081</v>
       </c>
       <c r="C58" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3355,59 +3405,111 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="B59" s="2">
-        <v>0.01077789440751076</v>
+        <v>0.0104681896045804</v>
       </c>
       <c r="C59" s="1">
         <v>4</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
         <v>4</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
       <c r="H59" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.0104681896045804</v>
+      </c>
+      <c r="C60" s="1">
+        <v>4</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60">
+      <c r="B61" s="2">
+        <v>0.0104681896045804</v>
+      </c>
+      <c r="C61" s="1">
+        <v>4</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>4</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C60">
+      <c r="C62">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D60">
+      <c r="D62">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E60">
+      <c r="E62">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F60">
+      <c r="F62">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G60">
+      <c r="G62">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H60">
+      <c r="H62">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/LED/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/LED/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>atk_f407</t>
   </si>
@@ -47,6 +47,9 @@
     <t>usart.o</t>
   </si>
   <si>
+    <t>lcd.o</t>
+  </si>
+  <si>
     <t>can.o</t>
   </si>
   <si>
@@ -113,6 +116,9 @@
     <t>dadd.o</t>
   </si>
   <si>
+    <t>stm32f4xx_ll_fsmc.o</t>
+  </si>
+  <si>
     <t>dmul.o</t>
   </si>
   <si>
@@ -131,24 +137,30 @@
     <t>usbd_ioreq.o</t>
   </si>
   <si>
+    <t>led.o</t>
+  </si>
+  <si>
     <t>list.o</t>
   </si>
   <si>
-    <t>led.o</t>
-  </si>
-  <si>
     <t>uldiv.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_pcd_ex.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_sram.o</t>
+  </si>
+  <si>
     <t>__dczerorl2.o</t>
   </si>
   <si>
     <t>main.o</t>
   </si>
   <si>
+    <t>dfixui.o</t>
+  </si>
+  <si>
     <t>dfixul.o</t>
   </si>
   <si>
@@ -177,6 +189,9 @@
   </si>
   <si>
     <t>handlers.o</t>
+  </si>
+  <si>
+    <t>dfltui.o</t>
   </si>
   <si>
     <t>stm32f4xx_it.o</t>
@@ -314,9 +329,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$62</c:f>
+              <c:f>ram_percent!$A$3:$A$67</c:f>
               <c:strCache>
-                <c:ptCount val="60"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -345,39 +360,42 @@
                   <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>lcd.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="64">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -385,71 +403,74 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$62</c:f>
+              <c:f>ram_percent!$B$3:$B$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
-                  <c:v>55.02119827270508</c:v>
+                  <c:v>54.96340179443359</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.98826599121094</c:v>
+                  <c:v>38.94731140136719</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.51245653629303</c:v>
+                  <c:v>1.510867714881897</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.15559732913971</c:v>
+                  <c:v>1.154383420944214</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.14552915096283</c:v>
+                  <c:v>1.144325852394104</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8994194269180298</c:v>
+                  <c:v>0.8984746336936951</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3736394047737122</c:v>
+                  <c:v>0.3732469081878662</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3031625151634216</c:v>
+                  <c:v>0.3028440475463867</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3031625151634216</c:v>
+                  <c:v>0.3028440475463867</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1029186397790909</c:v>
+                  <c:v>0.1050455346703529</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.07159557193517685</c:v>
+                  <c:v>0.1028105244040489</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.06712085008621216</c:v>
+                  <c:v>0.0715203657746315</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.01342417020350695</c:v>
+                  <c:v>0.06705034524202347</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01342417020350695</c:v>
+                  <c:v>0.01341006904840469</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01006812788546085</c:v>
+                  <c:v>0.01341006904840469</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.004474723245948553</c:v>
+                  <c:v>0.01005755178630352</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.004474723245948553</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.004474723245948553</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004474723245948553</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.001118680811487138</c:v>
-                </c:pt>
-                <c:pt idx="59">
+                  <c:v>0.004470022860914469</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.001117505715228617</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -517,187 +538,202 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$62</c:f>
+              <c:f>flash_percent!$A$3:$A$67</c:f>
               <c:strCache>
-                <c:ptCount val="60"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
+                  <c:v>lcd.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>stm32f4xx_ll_usb.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>stm32f4xx_hal_pcd.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>stm32f4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>usbd_cdc.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>timers.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>timers.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>usbd_core.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>stm32f4xx_hal_can.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>malloc.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>usbd_desc.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>usbd_cdc_interface.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
+                  <c:v>stm32f4xx_ll_fsmc.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>sys.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="35">
+                  <c:v>delay.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="37">
+                  <c:v>led.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
-                  <c:v>led.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="39">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="40">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="41">
+                  <c:v>stm32f4xx_hal_sram.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
-                  <c:v>delay.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="43">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="44">
+                  <c:v>dfixui.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="46">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="47">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="48">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="49">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="50">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="51">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="52">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="53">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="54">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="55">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="56">
+                  <c:v>dfltui.o</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="58">
                   <c:v>fputc.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="59">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="60">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="61">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="62">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="63">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="64">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -705,188 +741,203 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$62</c:f>
+              <c:f>flash_percent!$B$3:$B$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
-                  <c:v>10.45248794555664</c:v>
+                  <c:v>25.46160125732422</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.918609619140625</c:v>
+                  <c:v>7.67383337020874</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.447829246520996</c:v>
+                  <c:v>7.281879901885986</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.139305591583252</c:v>
+                  <c:v>6.202086448669434</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.804611206054688</c:v>
+                  <c:v>5.241416454315186</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.66067361831665</c:v>
+                  <c:v>4.261532783508301</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.763026237487793</c:v>
+                  <c:v>4.155858993530273</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.700217247009277</c:v>
+                  <c:v>3.496839284896851</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.119232654571533</c:v>
+                  <c:v>3.450727224349976</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.268692255020142</c:v>
+                  <c:v>3.024189710617065</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.072413682937622</c:v>
+                  <c:v>2.399754047393799</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.883986234664917</c:v>
+                  <c:v>2.255653619766235</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.789772510528565</c:v>
+                  <c:v>2.194170713424683</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.627515554428101</c:v>
+                  <c:v>2.117316961288452</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.303001642227173</c:v>
+                  <c:v>1.929025650024414</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.164298295974731</c:v>
+                  <c:v>1.690779447555542</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.983721971511841</c:v>
+                  <c:v>1.588948488235474</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.507419347763062</c:v>
+                  <c:v>1.456375956535339</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.434141993522644</c:v>
+                  <c:v>1.10669207572937</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.339928269386292</c:v>
+                  <c:v>1.052894473075867</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.161969065666199</c:v>
+                  <c:v>0.9837262630462647</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.138415694236755</c:v>
+                  <c:v>0.8530750870704651</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.120096325874329</c:v>
+                  <c:v>0.835783064365387</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.900264322757721</c:v>
+                  <c:v>0.8223336338996887</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.8740938305854797</c:v>
+                  <c:v>0.6609410643577576</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.837455153465271</c:v>
+                  <c:v>0.6417276859283447</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6176232099533081</c:v>
+                  <c:v>0.614828884601593</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5966868400573731</c:v>
+                  <c:v>0.4688070416450501</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5836015939712524</c:v>
+                  <c:v>0.4457509517669678</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5809845328330994</c:v>
+                  <c:v>0.4380655884742737</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5495799779891968</c:v>
+                  <c:v>0.4284588992595673</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.5338776707649231</c:v>
+                  <c:v>0.4265375435352325</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4867708384990692</c:v>
+                  <c:v>0.4034814834594727</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4553662538528442</c:v>
+                  <c:v>0.3919534385204315</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3873230218887329</c:v>
+                  <c:v>0.3573693037033081</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3873230218887329</c:v>
+                  <c:v>0.3381558954715729</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.256470650434494</c:v>
+                  <c:v>0.3343132138252258</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2355342656373978</c:v>
+                  <c:v>0.2920437157154083</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2250660806894302</c:v>
+                  <c:v>0.2843583822250366</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2093637883663178</c:v>
+                  <c:v>0.1882913559675217</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1988956034183502</c:v>
+                  <c:v>0.1729206293821335</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1256182789802551</c:v>
+                  <c:v>0.1690779477357864</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1256182789802551</c:v>
+                  <c:v>0.1652352660894394</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.1256182789802551</c:v>
+                  <c:v>0.1537072211503983</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.115150086581707</c:v>
+                  <c:v>0.09606701880693436</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.09421370923519135</c:v>
+                  <c:v>0.09222433716058731</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.09421370923519135</c:v>
+                  <c:v>0.09222433716058731</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.09421370923519135</c:v>
+                  <c:v>0.09222433716058731</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.09421370923519135</c:v>
+                  <c:v>0.08453897386789322</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.08374551683664322</c:v>
+                  <c:v>0.06916825473308563</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.07851142436265945</c:v>
+                  <c:v>0.06916825473308563</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.07851142436265945</c:v>
+                  <c:v>0.06916825473308563</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.05234094709157944</c:v>
+                  <c:v>0.06916825473308563</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.04710685461759567</c:v>
+                  <c:v>0.06148289144039154</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.02093637920916081</c:v>
+                  <c:v>0.0576402097940445</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.02093637920916081</c:v>
+                  <c:v>0.0576402097940445</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.0104681896045804</c:v>
+                  <c:v>0.0499548502266407</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.0104681896045804</c:v>
+                  <c:v>0.03842680528759956</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.0104681896045804</c:v>
+                  <c:v>0.03458412736654282</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>0.01537072286009789</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.01537072286009789</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.007685361430048943</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.007685361430048943</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.007685361430048943</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -991,8 +1042,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H62" totalsRowCount="1">
-  <autoFilter ref="A2:H61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H67" totalsRowCount="1">
+  <autoFilter ref="A2:H66"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1008,8 +1059,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H62" totalsRowCount="1">
-  <autoFilter ref="A2:H61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H67" totalsRowCount="1">
+  <autoFilter ref="A2:H66"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1309,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1322,28 +1373,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1351,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>55.02119827270508</v>
+        <v>54.96340179443359</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -1377,7 +1428,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>38.98826599121094</v>
+        <v>38.94731140136719</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -1403,7 +1454,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.51245653629303</v>
+        <v>1.510867714881897</v>
       </c>
       <c r="C5" s="1">
         <v>1352</v>
@@ -1429,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.15559732913971</v>
+        <v>1.154383420944214</v>
       </c>
       <c r="C6" s="1">
         <v>1033</v>
@@ -1455,7 +1506,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.14552915096283</v>
+        <v>1.144325852394104</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -1481,7 +1532,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.8994194269180298</v>
+        <v>0.8984746336936951</v>
       </c>
       <c r="C8" s="1">
         <v>804</v>
@@ -1507,7 +1558,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.3736394047737122</v>
+        <v>0.3732469081878662</v>
       </c>
       <c r="C9" s="1">
         <v>334</v>
@@ -1533,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.3031625151634216</v>
+        <v>0.3028440475463867</v>
       </c>
       <c r="C10" s="1">
         <v>271</v>
@@ -1559,7 +1610,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3031625151634216</v>
+        <v>0.3028440475463867</v>
       </c>
       <c r="C11" s="1">
         <v>271</v>
@@ -1585,16 +1636,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1029186397790909</v>
+        <v>0.1050455346703529</v>
       </c>
       <c r="C12" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1">
-        <v>320</v>
+        <v>13252</v>
       </c>
       <c r="E12" s="1">
-        <v>320</v>
+        <v>13252</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1603,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1611,16 +1662,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.07159557193517685</v>
+        <v>0.1028105244040489</v>
       </c>
       <c r="C13" s="1">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1">
-        <v>1574</v>
+        <v>320</v>
       </c>
       <c r="E13" s="1">
-        <v>1574</v>
+        <v>320</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1629,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1637,25 +1688,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.06712085008621216</v>
+        <v>0.0715203657746315</v>
       </c>
       <c r="C14" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D14" s="1">
-        <v>1102</v>
+        <v>1574</v>
       </c>
       <c r="E14" s="1">
-        <v>1082</v>
+        <v>1574</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1663,25 +1714,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.01342417020350695</v>
+        <v>0.06705034524202347</v>
       </c>
       <c r="C15" s="1">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D15" s="1">
-        <v>1174</v>
+        <v>1102</v>
       </c>
       <c r="E15" s="1">
-        <v>1162</v>
+        <v>1082</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1689,16 +1740,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01342417020350695</v>
+        <v>0.01341006904840469</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>236</v>
+        <v>1174</v>
       </c>
       <c r="E16" s="1">
-        <v>224</v>
+        <v>1162</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1715,22 +1766,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01006812788546085</v>
+        <v>0.01341006904840469</v>
       </c>
       <c r="C17" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="E17" s="1">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1741,22 +1792,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.004474723245948553</v>
+        <v>0.01005755178630352</v>
       </c>
       <c r="C18" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1">
-        <v>2728</v>
+        <v>223</v>
       </c>
       <c r="E18" s="1">
-        <v>2724</v>
+        <v>214</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1767,16 +1818,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.004474723245948553</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>4</v>
+        <v>2728</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>2724</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1793,19 +1844,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.004474723245948553</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>4</v>
@@ -1819,19 +1870,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004474723245948553</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="E21" s="1">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G21" s="1">
         <v>4</v>
@@ -1845,56 +1896,82 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.001118680811487138</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C22" s="1">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1">
+        <v>176</v>
+      </c>
+      <c r="E22" s="1">
+        <v>172</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.001117505715228617</v>
+      </c>
+      <c r="C23" s="1">
         <v>1</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D23" s="1">
         <v>2163</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E23" s="1">
         <v>2162</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
         <v>1</v>
       </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62">
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C62">
+      <c r="C67">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D62">
+      <c r="D67">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E62">
+      <c r="E67">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F62">
+      <c r="F67">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G62">
+      <c r="G67">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H62">
+      <c r="H67">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1910,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1923,80 +2000,80 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>10.45248794555664</v>
+        <v>25.46160125732422</v>
       </c>
       <c r="C3" s="1">
-        <v>3994</v>
+        <v>13252</v>
       </c>
       <c r="D3" s="1">
-        <v>804</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1">
-        <v>3930</v>
+        <v>13252</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>740</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>9.918609619140625</v>
+        <v>7.67383337020874</v>
       </c>
       <c r="C4" s="1">
-        <v>3790</v>
+        <v>3994</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="E4" s="1">
-        <v>3790</v>
+        <v>3930</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>740</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2004,16 +2081,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>8.447829246520996</v>
+        <v>7.281879901885986</v>
       </c>
       <c r="C5" s="1">
-        <v>3228</v>
+        <v>3790</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>3228</v>
+        <v>3790</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2027,25 +2104,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
-        <v>7.139305591583252</v>
+        <v>6.202086448669434</v>
       </c>
       <c r="C6" s="1">
-        <v>2728</v>
+        <v>3228</v>
       </c>
       <c r="D6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2724</v>
+        <v>3228</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -2053,25 +2130,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>5.804611206054688</v>
+        <v>5.241416454315186</v>
       </c>
       <c r="C7" s="1">
-        <v>2218</v>
+        <v>2728</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>2218</v>
+        <v>2724</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -2079,25 +2156,25 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>5.66067361831665</v>
+        <v>4.261532783508301</v>
       </c>
       <c r="C8" s="1">
-        <v>2163</v>
+        <v>2218</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2162</v>
+        <v>2218</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -2105,25 +2182,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="2">
-        <v>4.763026237487793</v>
+        <v>4.155858993530273</v>
       </c>
       <c r="C9" s="1">
-        <v>1820</v>
+        <v>2163</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>1820</v>
+        <v>2162</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2134,16 +2211,16 @@
         <v>25</v>
       </c>
       <c r="B10" s="2">
-        <v>4.700217247009277</v>
+        <v>3.496839284896851</v>
       </c>
       <c r="C10" s="1">
-        <v>1796</v>
+        <v>1820</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>1796</v>
+        <v>1820</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -2157,19 +2234,19 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>4.119232654571533</v>
+        <v>3.450727224349976</v>
       </c>
       <c r="C11" s="1">
-        <v>1574</v>
+        <v>1796</v>
       </c>
       <c r="D11" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>1574</v>
+        <v>1796</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -2178,56 +2255,56 @@
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>3.268692255020142</v>
+        <v>3.024189710617065</v>
       </c>
       <c r="C12" s="1">
-        <v>1249</v>
+        <v>1574</v>
       </c>
       <c r="D12" s="1">
-        <v>271</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1">
-        <v>978</v>
+        <v>1574</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
-        <v>3.072413682937622</v>
+        <v>2.399754047393799</v>
       </c>
       <c r="C13" s="1">
-        <v>1174</v>
+        <v>1249</v>
       </c>
       <c r="D13" s="1">
-        <v>12</v>
+        <v>271</v>
       </c>
       <c r="E13" s="1">
-        <v>1162</v>
+        <v>978</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>12</v>
+        <v>271</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -2235,45 +2312,45 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2.255653619766235</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1174</v>
+      </c>
+      <c r="D14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
-        <v>2.883986234664917</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1102</v>
-      </c>
-      <c r="D14" s="1">
-        <v>60</v>
-      </c>
       <c r="E14" s="1">
-        <v>1082</v>
+        <v>1162</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H14" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2">
-        <v>2.789772510528565</v>
+        <v>2.194170713424683</v>
       </c>
       <c r="C15" s="1">
-        <v>1066</v>
+        <v>1142</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1066</v>
+        <v>1142</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2287,288 +2364,288 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2">
-        <v>2.627515554428101</v>
+        <v>2.117316961288452</v>
       </c>
       <c r="C16" s="1">
-        <v>1004</v>
+        <v>1102</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E16" s="1">
-        <v>1004</v>
+        <v>1082</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2">
-        <v>2.303001642227173</v>
+        <v>1.929025650024414</v>
       </c>
       <c r="C17" s="1">
-        <v>880</v>
+        <v>1004</v>
       </c>
       <c r="D17" s="1">
-        <v>49184</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>848</v>
+        <v>1004</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>49152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>2.164298295974731</v>
+        <v>1.690779447555542</v>
       </c>
       <c r="C18" s="1">
-        <v>827</v>
+        <v>880</v>
       </c>
       <c r="D18" s="1">
-        <v>1033</v>
+        <v>49184</v>
       </c>
       <c r="E18" s="1">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H18" s="1">
-        <v>1032</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>1.983721971511841</v>
+        <v>1.588948488235474</v>
       </c>
       <c r="C19" s="1">
-        <v>758</v>
+        <v>827</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="E19" s="1">
-        <v>758</v>
+        <v>826</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2">
-        <v>1.507419347763062</v>
+        <v>1.456375956535339</v>
       </c>
       <c r="C20" s="1">
-        <v>576</v>
+        <v>758</v>
       </c>
       <c r="D20" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>504</v>
+        <v>758</v>
       </c>
       <c r="F20" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B21" s="2">
-        <v>1.434141993522644</v>
+        <v>1.10669207572937</v>
       </c>
       <c r="C21" s="1">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>34852</v>
       </c>
       <c r="E21" s="1">
-        <v>548</v>
+        <v>504</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B22" s="2">
-        <v>1.339928269386292</v>
+        <v>1.052894473075867</v>
       </c>
       <c r="C22" s="1">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D22" s="1">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>434</v>
+        <v>548</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>1.161969065666199</v>
+        <v>0.9837262630462647</v>
       </c>
       <c r="C23" s="1">
-        <v>444</v>
+        <v>512</v>
       </c>
       <c r="D23" s="1">
-        <v>1024</v>
+        <v>334</v>
       </c>
       <c r="E23" s="1">
-        <v>52</v>
+        <v>434</v>
       </c>
       <c r="F23" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H23" s="1">
-        <v>1024</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B24" s="2">
-        <v>1.138415694236755</v>
+        <v>0.8530750870704651</v>
       </c>
       <c r="C24" s="1">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D24" s="1">
-        <v>271</v>
+        <v>1024</v>
       </c>
       <c r="E24" s="1">
-        <v>432</v>
+        <v>52</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G24" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>268</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.835783064365387</v>
+      </c>
+      <c r="C25" s="1">
+        <v>435</v>
+      </c>
+      <c r="D25" s="1">
+        <v>271</v>
+      </c>
+      <c r="E25" s="1">
+        <v>432</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
         <v>3</v>
       </c>
-      <c r="B25" s="2">
-        <v>1.120096325874329</v>
-      </c>
-      <c r="C25" s="1">
-        <v>428</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1352</v>
-      </c>
-      <c r="E25" s="1">
-        <v>396</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>32</v>
-      </c>
       <c r="H25" s="1">
-        <v>1320</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B26" s="2">
-        <v>0.900264322757721</v>
+        <v>0.8223336338996887</v>
       </c>
       <c r="C26" s="1">
-        <v>344</v>
+        <v>428</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="E26" s="1">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2576,16 +2653,16 @@
         <v>31</v>
       </c>
       <c r="B27" s="2">
-        <v>0.8740938305854797</v>
+        <v>0.6609410643577576</v>
       </c>
       <c r="C27" s="1">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2599,19 +2676,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2">
-        <v>0.837455153465271</v>
+        <v>0.6417276859283447</v>
       </c>
       <c r="C28" s="1">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D28" s="1">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2620,56 +2697,56 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6176232099533081</v>
+        <v>0.614828884601593</v>
       </c>
       <c r="C29" s="1">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="D29" s="1">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="E29" s="1">
-        <v>224</v>
+        <v>320</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5966868400573731</v>
+        <v>0.4688070416450501</v>
       </c>
       <c r="C30" s="1">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2677,25 +2754,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5836015939712524</v>
+        <v>0.4457509517669678</v>
       </c>
       <c r="C31" s="1">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D31" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2703,19 +2780,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5809845328330994</v>
+        <v>0.4380655884742737</v>
       </c>
       <c r="C32" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2729,25 +2806,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5495799779891968</v>
+        <v>0.4284588992595673</v>
       </c>
       <c r="C33" s="1">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2758,16 +2835,16 @@
         <v>35</v>
       </c>
       <c r="B34" s="2">
-        <v>0.5338776707649231</v>
+        <v>0.4265375435352325</v>
       </c>
       <c r="C34" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2784,16 +2861,16 @@
         <v>36</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4867708384990692</v>
+        <v>0.4034814834594727</v>
       </c>
       <c r="C35" s="1">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2810,16 +2887,16 @@
         <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4553662538528442</v>
+        <v>0.3919534385204315</v>
       </c>
       <c r="C36" s="1">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2836,16 +2913,16 @@
         <v>38</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3873230218887329</v>
+        <v>0.3573693037033081</v>
       </c>
       <c r="C37" s="1">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2859,25 +2936,25 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3873230218887329</v>
+        <v>0.3381558954715729</v>
       </c>
       <c r="C38" s="1">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E38" s="1">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -2885,19 +2962,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.256470650434494</v>
+        <v>0.3343132138252258</v>
       </c>
       <c r="C39" s="1">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2911,19 +2988,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2355342656373978</v>
+        <v>0.2920437157154083</v>
       </c>
       <c r="C40" s="1">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2937,19 +3014,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2250660806894302</v>
+        <v>0.2843583822250366</v>
       </c>
       <c r="C41" s="1">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2963,25 +3040,25 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2093637883663178</v>
+        <v>0.1882913559675217</v>
       </c>
       <c r="C42" s="1">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D42" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -2992,16 +3069,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1988956034183502</v>
+        <v>0.1729206293821335</v>
       </c>
       <c r="C43" s="1">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3018,16 +3095,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1256182789802551</v>
+        <v>0.1690779477357864</v>
       </c>
       <c r="C44" s="1">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3044,16 +3121,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1256182789802551</v>
+        <v>0.1652352660894394</v>
       </c>
       <c r="C45" s="1">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3067,25 +3144,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.1256182789802551</v>
+        <v>0.1537072211503983</v>
       </c>
       <c r="C46" s="1">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F46" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -3093,19 +3170,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.115150086581707</v>
+        <v>0.09606701880693436</v>
       </c>
       <c r="C47" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3119,19 +3196,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.09421370923519135</v>
+        <v>0.09222433716058731</v>
       </c>
       <c r="C48" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3145,19 +3222,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.09222433716058731</v>
+      </c>
+      <c r="C49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="2">
-        <v>0.09421370923519135</v>
-      </c>
-      <c r="C49" s="1">
-        <v>36</v>
-      </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3171,25 +3248,25 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B50" s="2">
-        <v>0.09421370923519135</v>
+        <v>0.09222433716058731</v>
       </c>
       <c r="C50" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E50" s="1">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -3200,16 +3277,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.09421370923519135</v>
+        <v>0.08453897386789322</v>
       </c>
       <c r="C51" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3226,16 +3303,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.08374551683664322</v>
+        <v>0.06916825473308563</v>
       </c>
       <c r="C52" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3252,16 +3329,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.07851142436265945</v>
+        <v>0.06916825473308563</v>
       </c>
       <c r="C53" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3278,16 +3355,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.07851142436265945</v>
+        <v>0.06916825473308563</v>
       </c>
       <c r="C54" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3304,16 +3381,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.05234094709157944</v>
+        <v>0.06916825473308563</v>
       </c>
       <c r="C55" s="1">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3330,16 +3407,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.04710685461759567</v>
+        <v>0.06148289144039154</v>
       </c>
       <c r="C56" s="1">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3356,16 +3433,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.02093637920916081</v>
+        <v>0.0576402097940445</v>
       </c>
       <c r="C57" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3382,16 +3459,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.02093637920916081</v>
+        <v>0.0576402097940445</v>
       </c>
       <c r="C58" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3405,25 +3482,25 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.0104681896045804</v>
+        <v>0.0499548502266407</v>
       </c>
       <c r="C59" s="1">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -3431,19 +3508,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2">
-        <v>0.0104681896045804</v>
+        <v>0.03842680528759956</v>
       </c>
       <c r="C60" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3457,59 +3534,189 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>0.0104681896045804</v>
+        <v>0.03458412736654282</v>
       </c>
       <c r="C61" s="1">
+        <v>18</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>18</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0.01537072286009789</v>
+      </c>
+      <c r="C62" s="1">
+        <v>8</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>8</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.01537072286009789</v>
+      </c>
+      <c r="C63" s="1">
+        <v>8</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>8</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.007685361430048943</v>
+      </c>
+      <c r="C64" s="1">
         <v>4</v>
       </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D64" s="1">
         <v>4</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62">
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>4</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.007685361430048943</v>
+      </c>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>4</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.007685361430048943</v>
+      </c>
+      <c r="C66" s="1">
+        <v>4</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>4</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C62">
+      <c r="C67">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D62">
+      <c r="D67">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E62">
+      <c r="E67">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F62">
+      <c r="F67">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G62">
+      <c r="G67">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H62">
+      <c r="H67">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/LED/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/LED/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -623,19 +623,19 @@
                   <c:v>can.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>stm32f4xx_ll_fsmc.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>stm32f4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>ddiv.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>freertos_start.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>stm32f4xx_ll_fsmc.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>dmul.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>stm32f4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>ddiv.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
@@ -746,196 +746,196 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="65"/>
                 <c:pt idx="0">
-                  <c:v>25.46160125732422</c:v>
+                  <c:v>25.47530746459961</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.67383337020874</c:v>
+                  <c:v>7.677963733673096</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.281879901885986</c:v>
+                  <c:v>7.285799503326416</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.202086448669434</c:v>
+                  <c:v>6.205424785614014</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.241416454315186</c:v>
+                  <c:v>5.244237899780273</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.261532783508301</c:v>
+                  <c:v>4.263826847076416</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.155858993530273</c:v>
+                  <c:v>4.158096313476563</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.496839284896851</c:v>
+                  <c:v>3.498721599578857</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.450727224349976</c:v>
+                  <c:v>3.452584743499756</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.024189710617065</c:v>
+                  <c:v>3.025817394256592</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.399754047393799</c:v>
+                  <c:v>2.401045799255371</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.255653619766235</c:v>
+                  <c:v>2.256867647171021</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.194170713424683</c:v>
+                  <c:v>2.195351600646973</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.117316961288452</c:v>
+                  <c:v>2.118456602096558</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.929025650024414</c:v>
+                  <c:v>1.930063962936401</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.690779447555542</c:v>
+                  <c:v>1.691689610481262</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.588948488235474</c:v>
+                  <c:v>1.589803695678711</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.456375956535339</c:v>
+                  <c:v>1.457159876823425</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.10669207572937</c:v>
+                  <c:v>1.107287764549255</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.052894473075867</c:v>
+                  <c:v>1.053461194038391</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9837262630462647</c:v>
+                  <c:v>0.9842557311058044</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8530750870704651</c:v>
+                  <c:v>0.8535342812538147</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.835783064365387</c:v>
+                  <c:v>0.8362329006195068</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8223336338996887</c:v>
+                  <c:v>0.8227763175964356</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6609410643577576</c:v>
+                  <c:v>0.6612968444824219</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6417276859283447</c:v>
+                  <c:v>0.6420730948448181</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.614828884601593</c:v>
+                  <c:v>0.6151598691940308</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.4688070416450501</c:v>
+                  <c:v>0.4459908902645111</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.4457509517669678</c:v>
+                  <c:v>0.4383013844490051</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4380655884742737</c:v>
+                  <c:v>0.4286895096302033</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4284588992595673</c:v>
+                  <c:v>0.4267671406269074</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4265375435352325</c:v>
+                  <c:v>0.4229224026203156</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4034814834594727</c:v>
+                  <c:v>0.4036986529827118</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3919534385204315</c:v>
+                  <c:v>0.392164409160614</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3573693037033081</c:v>
+                  <c:v>0.3575616478919983</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3381558954715729</c:v>
+                  <c:v>0.3383379280567169</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3343132138252258</c:v>
+                  <c:v>0.3344931602478027</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2920437157154083</c:v>
+                  <c:v>0.2922009229660034</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2843583822250366</c:v>
+                  <c:v>0.2845114171504974</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1882913559675217</c:v>
+                  <c:v>0.188392698764801</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1729206293821335</c:v>
+                  <c:v>0.1730137020349503</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1690779477357864</c:v>
+                  <c:v>0.1691689640283585</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1652352660894394</c:v>
+                  <c:v>0.1653242111206055</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.1537072211503983</c:v>
+                  <c:v>0.1461004614830017</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09606701880693436</c:v>
+                  <c:v>0.09611872583627701</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.09222433716058731</c:v>
+                  <c:v>0.09227398037910461</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.09222433716058731</c:v>
+                  <c:v>0.09227398037910461</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.09222433716058731</c:v>
+                  <c:v>0.09227398037910461</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.08453897386789322</c:v>
+                  <c:v>0.08458448201417923</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.06916825473308563</c:v>
+                  <c:v>0.06920548528432846</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.06916825473308563</c:v>
+                  <c:v>0.06920548528432846</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.06916825473308563</c:v>
+                  <c:v>0.06920548528432846</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.06916825473308563</c:v>
+                  <c:v>0.06920548528432846</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.06148289144039154</c:v>
+                  <c:v>0.06151598319411278</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.0576402097940445</c:v>
+                  <c:v>0.05767123401165009</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.0576402097940445</c:v>
+                  <c:v>0.05767123401165009</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.0499548502266407</c:v>
+                  <c:v>0.0499817356467247</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.03842680528759956</c:v>
+                  <c:v>0.03844749182462692</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.03458412736654282</c:v>
+                  <c:v>0.03460274264216423</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.01537072286009789</c:v>
+                  <c:v>0.01537899579852819</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.01537072286009789</c:v>
+                  <c:v>0.01537899579852819</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.007685361430048943</c:v>
+                  <c:v>0.007689497899264097</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.007685361430048943</c:v>
+                  <c:v>0.007689497899264097</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.007685361430048943</c:v>
+                  <c:v>0.007689497899264097</c:v>
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0</c:v>
@@ -1772,10 +1772,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E17" s="1">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>25.46160125732422</v>
+        <v>25.47530746459961</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2055,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>7.67383337020874</v>
+        <v>7.677963733673096</v>
       </c>
       <c r="C4" s="1">
         <v>3994</v>
@@ -2081,7 +2081,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>7.281879901885986</v>
+        <v>7.285799503326416</v>
       </c>
       <c r="C5" s="1">
         <v>3790</v>
@@ -2107,7 +2107,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="2">
-        <v>6.202086448669434</v>
+        <v>6.205424785614014</v>
       </c>
       <c r="C6" s="1">
         <v>3228</v>
@@ -2133,7 +2133,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>5.241416454315186</v>
+        <v>5.244237899780273</v>
       </c>
       <c r="C7" s="1">
         <v>2728</v>
@@ -2159,7 +2159,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>4.261532783508301</v>
+        <v>4.263826847076416</v>
       </c>
       <c r="C8" s="1">
         <v>2218</v>
@@ -2185,7 +2185,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="2">
-        <v>4.155858993530273</v>
+        <v>4.158096313476563</v>
       </c>
       <c r="C9" s="1">
         <v>2163</v>
@@ -2211,7 +2211,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2">
-        <v>3.496839284896851</v>
+        <v>3.498721599578857</v>
       </c>
       <c r="C10" s="1">
         <v>1820</v>
@@ -2237,7 +2237,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>3.450727224349976</v>
+        <v>3.452584743499756</v>
       </c>
       <c r="C11" s="1">
         <v>1796</v>
@@ -2263,7 +2263,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>3.024189710617065</v>
+        <v>3.025817394256592</v>
       </c>
       <c r="C12" s="1">
         <v>1574</v>
@@ -2289,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2">
-        <v>2.399754047393799</v>
+        <v>2.401045799255371</v>
       </c>
       <c r="C13" s="1">
         <v>1249</v>
@@ -2315,7 +2315,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>2.255653619766235</v>
+        <v>2.256867647171021</v>
       </c>
       <c r="C14" s="1">
         <v>1174</v>
@@ -2341,7 +2341,7 @@
         <v>27</v>
       </c>
       <c r="B15" s="2">
-        <v>2.194170713424683</v>
+        <v>2.195351600646973</v>
       </c>
       <c r="C15" s="1">
         <v>1142</v>
@@ -2367,7 +2367,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2">
-        <v>2.117316961288452</v>
+        <v>2.118456602096558</v>
       </c>
       <c r="C16" s="1">
         <v>1102</v>
@@ -2393,7 +2393,7 @@
         <v>28</v>
       </c>
       <c r="B17" s="2">
-        <v>1.929025650024414</v>
+        <v>1.930063962936401</v>
       </c>
       <c r="C17" s="1">
         <v>1004</v>
@@ -2419,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>1.690779447555542</v>
+        <v>1.691689610481262</v>
       </c>
       <c r="C18" s="1">
         <v>880</v>
@@ -2445,7 +2445,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>1.588948488235474</v>
+        <v>1.589803695678711</v>
       </c>
       <c r="C19" s="1">
         <v>827</v>
@@ -2471,7 +2471,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2">
-        <v>1.456375956535339</v>
+        <v>1.457159876823425</v>
       </c>
       <c r="C20" s="1">
         <v>758</v>
@@ -2497,7 +2497,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="2">
-        <v>1.10669207572937</v>
+        <v>1.107287764549255</v>
       </c>
       <c r="C21" s="1">
         <v>576</v>
@@ -2523,7 +2523,7 @@
         <v>30</v>
       </c>
       <c r="B22" s="2">
-        <v>1.052894473075867</v>
+        <v>1.053461194038391</v>
       </c>
       <c r="C22" s="1">
         <v>548</v>
@@ -2549,7 +2549,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9837262630462647</v>
+        <v>0.9842557311058044</v>
       </c>
       <c r="C23" s="1">
         <v>512</v>
@@ -2575,7 +2575,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8530750870704651</v>
+        <v>0.8535342812538147</v>
       </c>
       <c r="C24" s="1">
         <v>444</v>
@@ -2601,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="2">
-        <v>0.835783064365387</v>
+        <v>0.8362329006195068</v>
       </c>
       <c r="C25" s="1">
         <v>435</v>
@@ -2627,7 +2627,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8223336338996887</v>
+        <v>0.8227763175964356</v>
       </c>
       <c r="C26" s="1">
         <v>428</v>
@@ -2653,7 +2653,7 @@
         <v>31</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6609410643577576</v>
+        <v>0.6612968444824219</v>
       </c>
       <c r="C27" s="1">
         <v>344</v>
@@ -2679,7 +2679,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6417276859283447</v>
+        <v>0.6420730948448181</v>
       </c>
       <c r="C28" s="1">
         <v>334</v>
@@ -2705,7 +2705,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="2">
-        <v>0.614828884601593</v>
+        <v>0.6151598691940308</v>
       </c>
       <c r="C29" s="1">
         <v>320</v>
@@ -2728,16 +2728,16 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2">
-        <v>0.4688070416450501</v>
+        <v>0.4459908902645111</v>
       </c>
       <c r="C30" s="1">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D30" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
         <v>232</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2754,19 +2754,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2">
-        <v>0.4457509517669678</v>
+        <v>0.4383013844490051</v>
       </c>
       <c r="C31" s="1">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2780,25 +2780,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4380655884742737</v>
+        <v>0.4286895096302033</v>
       </c>
       <c r="C32" s="1">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2806,25 +2806,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4284588992595673</v>
+        <v>0.4267671406269074</v>
       </c>
       <c r="C33" s="1">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D33" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2832,25 +2832,25 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4265375435352325</v>
+        <v>0.4229224026203156</v>
       </c>
       <c r="C34" s="1">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E34" s="1">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4034814834594727</v>
+        <v>0.4036986529827118</v>
       </c>
       <c r="C35" s="1">
         <v>210</v>
@@ -2887,7 +2887,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3919534385204315</v>
+        <v>0.392164409160614</v>
       </c>
       <c r="C36" s="1">
         <v>204</v>
@@ -2913,7 +2913,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3573693037033081</v>
+        <v>0.3575616478919983</v>
       </c>
       <c r="C37" s="1">
         <v>186</v>
@@ -2939,7 +2939,7 @@
         <v>20</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3381558954715729</v>
+        <v>0.3383379280567169</v>
       </c>
       <c r="C38" s="1">
         <v>176</v>
@@ -2965,7 +2965,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3343132138252258</v>
+        <v>0.3344931602478027</v>
       </c>
       <c r="C39" s="1">
         <v>174</v>
@@ -2991,7 +2991,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2920437157154083</v>
+        <v>0.2922009229660034</v>
       </c>
       <c r="C40" s="1">
         <v>152</v>
@@ -3017,7 +3017,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2843583822250366</v>
+        <v>0.2845114171504974</v>
       </c>
       <c r="C41" s="1">
         <v>148</v>
@@ -3043,7 +3043,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1882913559675217</v>
+        <v>0.188392698764801</v>
       </c>
       <c r="C42" s="1">
         <v>98</v>
@@ -3069,7 +3069,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1729206293821335</v>
+        <v>0.1730137020349503</v>
       </c>
       <c r="C43" s="1">
         <v>90</v>
@@ -3095,7 +3095,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1690779477357864</v>
+        <v>0.1691689640283585</v>
       </c>
       <c r="C44" s="1">
         <v>88</v>
@@ -3121,7 +3121,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1652352660894394</v>
+        <v>0.1653242111206055</v>
       </c>
       <c r="C45" s="1">
         <v>86</v>
@@ -3147,16 +3147,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.1537072211503983</v>
+        <v>0.1461004614830017</v>
       </c>
       <c r="C46" s="1">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3173,7 +3173,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.09606701880693436</v>
+        <v>0.09611872583627701</v>
       </c>
       <c r="C47" s="1">
         <v>50</v>
@@ -3199,7 +3199,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.09222433716058731</v>
+        <v>0.09227398037910461</v>
       </c>
       <c r="C48" s="1">
         <v>48</v>
@@ -3225,7 +3225,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.09222433716058731</v>
+        <v>0.09227398037910461</v>
       </c>
       <c r="C49" s="1">
         <v>48</v>
@@ -3251,7 +3251,7 @@
         <v>19</v>
       </c>
       <c r="B50" s="2">
-        <v>0.09222433716058731</v>
+        <v>0.09227398037910461</v>
       </c>
       <c r="C50" s="1">
         <v>48</v>
@@ -3277,7 +3277,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.08453897386789322</v>
+        <v>0.08458448201417923</v>
       </c>
       <c r="C51" s="1">
         <v>44</v>
@@ -3303,7 +3303,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.06916825473308563</v>
+        <v>0.06920548528432846</v>
       </c>
       <c r="C52" s="1">
         <v>36</v>
@@ -3329,7 +3329,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.06916825473308563</v>
+        <v>0.06920548528432846</v>
       </c>
       <c r="C53" s="1">
         <v>36</v>
@@ -3355,7 +3355,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.06916825473308563</v>
+        <v>0.06920548528432846</v>
       </c>
       <c r="C54" s="1">
         <v>36</v>
@@ -3381,7 +3381,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.06916825473308563</v>
+        <v>0.06920548528432846</v>
       </c>
       <c r="C55" s="1">
         <v>36</v>
@@ -3407,7 +3407,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.06148289144039154</v>
+        <v>0.06151598319411278</v>
       </c>
       <c r="C56" s="1">
         <v>32</v>
@@ -3433,7 +3433,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.0576402097940445</v>
+        <v>0.05767123401165009</v>
       </c>
       <c r="C57" s="1">
         <v>30</v>
@@ -3459,7 +3459,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.0576402097940445</v>
+        <v>0.05767123401165009</v>
       </c>
       <c r="C58" s="1">
         <v>30</v>
@@ -3485,7 +3485,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.0499548502266407</v>
+        <v>0.0499817356467247</v>
       </c>
       <c r="C59" s="1">
         <v>26</v>
@@ -3511,7 +3511,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2">
-        <v>0.03842680528759956</v>
+        <v>0.03844749182462692</v>
       </c>
       <c r="C60" s="1">
         <v>20</v>
@@ -3537,7 +3537,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>0.03458412736654282</v>
+        <v>0.03460274264216423</v>
       </c>
       <c r="C61" s="1">
         <v>18</v>
@@ -3563,7 +3563,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2">
-        <v>0.01537072286009789</v>
+        <v>0.01537899579852819</v>
       </c>
       <c r="C62" s="1">
         <v>8</v>
@@ -3589,7 +3589,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2">
-        <v>0.01537072286009789</v>
+        <v>0.01537899579852819</v>
       </c>
       <c r="C63" s="1">
         <v>8</v>
@@ -3615,7 +3615,7 @@
         <v>18</v>
       </c>
       <c r="B64" s="2">
-        <v>0.007685361430048943</v>
+        <v>0.007689497899264097</v>
       </c>
       <c r="C64" s="1">
         <v>4</v>
@@ -3641,7 +3641,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.007685361430048943</v>
+        <v>0.007689497899264097</v>
       </c>
       <c r="C65" s="1">
         <v>4</v>
@@ -3667,7 +3667,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.007685361430048943</v>
+        <v>0.007689497899264097</v>
       </c>
       <c r="C66" s="1">
         <v>4</v>
